--- a/Assignment 1 - Data Exploration.xlsx
+++ b/Assignment 1 - Data Exploration.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Neethu K S\Desktop\my works\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{181377F4-F2E7-489D-B130-D36D813DC13D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4815CC94-8A2E-44C9-8E0C-0858C0F4F182}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{F2338E2A-42BE-472D-826F-2DE3207B5E9C}"/>
   </bookViews>
@@ -2288,8 +2288,8 @@
         <v>US</v>
       </c>
       <c r="J2" s="18" t="str">
-        <f>MID(A2,4,6)</f>
-        <v>JAN-US</v>
+        <f>MID(A2,4,3)</f>
+        <v>JAN</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -2324,8 +2324,8 @@
         <v>US</v>
       </c>
       <c r="J3" s="18" t="str">
-        <f t="shared" ref="J3:J35" si="3">MID(A3,4,6)</f>
-        <v>FEB-US</v>
+        <f t="shared" ref="J3:J35" si="3">MID(A3,4,3)</f>
+        <v>FEB</v>
       </c>
       <c r="K3" s="6"/>
       <c r="L3" s="7"/>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="J4" s="18" t="str">
         <f t="shared" si="3"/>
-        <v>MAR-US</v>
+        <v>MAR</v>
       </c>
       <c r="K4" s="7"/>
       <c r="L4" s="8"/>
@@ -2405,7 +2405,7 @@
       </c>
       <c r="J5" s="18" t="str">
         <f t="shared" si="3"/>
-        <v>APR-US</v>
+        <v>APR</v>
       </c>
       <c r="K5" s="7"/>
       <c r="L5" s="8"/>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="J6" s="18" t="str">
         <f t="shared" si="3"/>
-        <v>MAY-US</v>
+        <v>MAY</v>
       </c>
       <c r="K6" s="7"/>
       <c r="L6" s="8"/>
@@ -2485,7 +2485,7 @@
       </c>
       <c r="J7" s="18" t="str">
         <f t="shared" si="3"/>
-        <v>JUN-UK</v>
+        <v>JUN</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -2521,7 +2521,7 @@
       </c>
       <c r="J8" s="18" t="str">
         <f t="shared" si="3"/>
-        <v>JUL-UK</v>
+        <v>JUL</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="J9" s="18" t="str">
         <f t="shared" si="3"/>
-        <v>AUG-UK</v>
+        <v>AUG</v>
       </c>
       <c r="K9" s="16">
         <v>1</v>
@@ -2603,7 +2603,7 @@
       </c>
       <c r="J10" s="18" t="str">
         <f t="shared" si="3"/>
-        <v>SEP-UK</v>
+        <v>SEP</v>
       </c>
       <c r="K10" s="16"/>
       <c r="L10" s="10" t="s">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="J11" s="18" t="str">
         <f t="shared" si="3"/>
-        <v>OCT-UK</v>
+        <v>OCT</v>
       </c>
       <c r="K11" s="16"/>
       <c r="L11" s="10" t="s">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="J12" s="18" t="str">
         <f t="shared" si="3"/>
-        <v>JUN-IN</v>
+        <v>JUN</v>
       </c>
       <c r="K12" s="16"/>
       <c r="L12" s="9"/>
@@ -2730,7 +2730,7 @@
       </c>
       <c r="J13" s="18" t="str">
         <f t="shared" si="3"/>
-        <v>NOV-AU</v>
+        <v>NOV</v>
       </c>
       <c r="K13" s="16">
         <v>2</v>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="J14" s="18" t="str">
         <f t="shared" si="3"/>
-        <v>DEC-DE</v>
+        <v>DEC</v>
       </c>
       <c r="K14" s="16"/>
       <c r="L14" s="10" t="s">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="J15" s="18" t="str">
         <f t="shared" si="3"/>
-        <v>FEB-CA</v>
+        <v>FEB</v>
       </c>
       <c r="K15" s="16"/>
       <c r="L15" s="9"/>
@@ -2859,7 +2859,7 @@
       </c>
       <c r="J16" s="18" t="str">
         <f t="shared" si="3"/>
-        <v>APR-ES</v>
+        <v>APR</v>
       </c>
       <c r="K16" s="16">
         <v>4</v>
@@ -2905,7 +2905,7 @@
       </c>
       <c r="J17" s="18" t="str">
         <f t="shared" si="3"/>
-        <v>AUG-CA</v>
+        <v>AUG</v>
       </c>
       <c r="K17" s="16"/>
       <c r="L17" s="12" t="s">
@@ -2950,7 +2950,7 @@
       </c>
       <c r="J18" s="18" t="str">
         <f t="shared" si="3"/>
-        <v>AUG-CN</v>
+        <v>AUG</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="J19" s="18" t="str">
         <f t="shared" si="3"/>
-        <v>JAN-IT</v>
+        <v>JAN</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="J20" s="18" t="str">
         <f t="shared" si="3"/>
-        <v>MAR-UK</v>
+        <v>MAR</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="J21" s="18" t="str">
         <f t="shared" si="3"/>
-        <v>AUG-US</v>
+        <v>AUG</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="J22" s="18" t="str">
         <f t="shared" si="3"/>
-        <v>MAY-RU</v>
+        <v>MAY</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -3130,7 +3130,7 @@
       </c>
       <c r="J23" s="18" t="str">
         <f t="shared" si="3"/>
-        <v>JAN-CA</v>
+        <v>JAN</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -3166,7 +3166,7 @@
       </c>
       <c r="J24" s="18" t="str">
         <f t="shared" si="3"/>
-        <v>JUL-BR</v>
+        <v>JUL</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="J25" s="18" t="str">
         <f t="shared" si="3"/>
-        <v>AUG-CA</v>
+        <v>AUG</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -3238,7 +3238,7 @@
       </c>
       <c r="J26" s="18" t="str">
         <f t="shared" si="3"/>
-        <v>SEP-CA</v>
+        <v>SEP</v>
       </c>
     </row>
     <row r="27" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="J27" s="18" t="str">
         <f t="shared" si="3"/>
-        <v>JUN-CA</v>
+        <v>JUN</v>
       </c>
     </row>
     <row r="28" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -3310,7 +3310,7 @@
       </c>
       <c r="J28" s="18" t="str">
         <f t="shared" si="3"/>
-        <v>JUL-CA</v>
+        <v>JUL</v>
       </c>
     </row>
     <row r="29" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -3346,7 +3346,7 @@
       </c>
       <c r="J29" s="18" t="str">
         <f t="shared" si="3"/>
-        <v>APR-ES</v>
+        <v>APR</v>
       </c>
     </row>
     <row r="30" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="J30" s="18" t="str">
         <f t="shared" si="3"/>
-        <v>MAR-CA</v>
+        <v>MAR</v>
       </c>
     </row>
     <row r="31" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="J31" s="18" t="str">
         <f t="shared" si="3"/>
-        <v>APR-CA</v>
+        <v>APR</v>
       </c>
     </row>
     <row r="32" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -3454,7 +3454,7 @@
       </c>
       <c r="J32" s="18" t="str">
         <f t="shared" si="3"/>
-        <v>MAY-CA</v>
+        <v>MAY</v>
       </c>
     </row>
     <row r="33" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -3490,7 +3490,7 @@
       </c>
       <c r="J33" s="18" t="str">
         <f t="shared" si="3"/>
-        <v>DEC-CA</v>
+        <v>DEC</v>
       </c>
     </row>
     <row r="34" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -3526,7 +3526,7 @@
       </c>
       <c r="J34" s="18" t="str">
         <f t="shared" si="3"/>
-        <v>JUN-IN</v>
+        <v>JUN</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="J35" s="18" t="str">
         <f t="shared" si="3"/>
-        <v>JUL-FR</v>
+        <v>JUL</v>
       </c>
     </row>
   </sheetData>
